--- a/01-Projects/네이버 블로그 - 3호 캠프닉 실행 계획.xlsx
+++ b/01-Projects/네이버 블로그 - 3호 캠프닉 실행 계획.xlsx
@@ -121,7 +121,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -139,6 +139,32 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <b val="1"/>
+        <color rgb="001B7A2F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <b val="1"/>
+        <color rgb="00C62828"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -526,7 +552,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>사용법: 완료한 항목의 [체크] 칸에 ✔ 를 입력하세요 (노란 칸 = 필수/직접 입력). 진행률이 자동 계산됩니다.</t>
+          <t>사용법: [체크] 칸을 클릭하면 드롭다운이 열립니다 — 완료 = O, 미완료 = X 선택. O는 초록, X는 빨강으로 표시되고 진행률이 자동 계산됩니다.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1119,7 @@
         </is>
       </c>
       <c r="C42" s="12">
-        <f>COUNTIF(A7:A40,"✔")&amp;" / 24 완료"</f>
+        <f>COUNTIF(A7:A40,"O")&amp;" / 24 완료"</f>
         <v/>
       </c>
     </row>
@@ -1109,6 +1135,19 @@
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A7:A40">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"O"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"X"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A7 A8 A9 A12 A13 A16 A17 A18 A19 A20 A21 A22 A23 A26 A27 A28 A29 A32 A33 A34 A37 A38 A39 A40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 입력" error="O 또는 X만 선택할 수 있습니다" type="list">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>